--- a/artfynd/A 20364-2026 artfynd.xlsx
+++ b/artfynd/A 20364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -784,6 +784,220 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133952810</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57958</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Norra Hammarskogen, Norra Hammarskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>504103</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6619186</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133952931</v>
+      </c>
+      <c r="B4" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Norra Hammarskogen, Norra Hammarskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>504125</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6619259</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lotta Sörman</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20364-2026 artfynd.xlsx
+++ b/artfynd/A 20364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -999,6 +999,148 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133951012</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57955</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Hammarskogsån, Lindes sn, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>503853</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6619264</v>
+      </c>
+      <c r="S5" t="n">
+        <v>6</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20364-2026 artfynd.xlsx
+++ b/artfynd/A 20364-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133472729</v>
       </c>
       <c r="B2" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133952810</v>
       </c>
       <c r="B3" t="n">
-        <v>57958</v>
+        <v>57965</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>133952931</v>
       </c>
       <c r="B4" t="n">
-        <v>5179</v>
+        <v>5181</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>133951012</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57962</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20364-2026 artfynd.xlsx
+++ b/artfynd/A 20364-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>133472729</v>
       </c>
       <c r="B2" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>133952810</v>
       </c>
       <c r="B3" t="n">
-        <v>57965</v>
+        <v>57975</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1004,7 +1004,7 @@
         <v>133951012</v>
       </c>
       <c r="B5" t="n">
-        <v>57962</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 20364-2026 artfynd.xlsx
+++ b/artfynd/A 20364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1141,6 +1141,116 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134220564</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Smedsjön, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>503672</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6619237</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-31</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Per Arneborn</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20364-2026 artfynd.xlsx
+++ b/artfynd/A 20364-2026 artfynd.xlsx
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>133472729</v>
+        <v>133472666</v>
       </c>
       <c r="B2" t="n">
         <v>57972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:34</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,27 +787,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133952810</v>
+        <v>133951012</v>
       </c>
       <c r="B3" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -816,19 +816,24 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Hammarskogen, Norra Hammarskogen, Vstm</t>
+          <t>Hammarskogsån, Lindes sn, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>504103</v>
+        <v>503853</v>
       </c>
       <c r="R3" t="n">
-        <v>6619186</v>
+        <v>6619264</v>
       </c>
       <c r="S3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:51</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,59 +872,89 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:51</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Färska hack i död gran</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Stående död trädstam/högstubbe</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Standing dead tree/snags # Picea abies</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lotta Sörman</t>
+          <t>Per Arneborn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133952931</v>
+        <v>133952810</v>
       </c>
       <c r="B4" t="n">
-        <v>5181</v>
+        <v>57975</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100526</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -929,10 +964,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>504125</v>
+        <v>504103</v>
       </c>
       <c r="R4" t="n">
-        <v>6619259</v>
+        <v>6619186</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,14 +1009,14 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG4" t="b">
         <v>0</v>
@@ -1001,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133951012</v>
+        <v>134220564</v>
       </c>
       <c r="B5" t="n">
-        <v>57972</v>
+        <v>57975</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1012,16 +1047,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1030,24 +1065,27 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Hammarskogsån, Lindes sn, Vstm</t>
+          <t>Smedsjön, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>503853</v>
+        <v>503672</v>
       </c>
       <c r="R5" t="n">
-        <v>6619264</v>
+        <v>6619237</v>
       </c>
       <c r="S5" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1071,27 +1109,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2026-05-30</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>10:51</t>
+          <t>2026-05-31</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Färska hack i död gran</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1102,31 +1130,6 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Stående död trädstam/högstubbe</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Standing dead tree/snags # Picea abies</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1143,56 +1146,48 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134220564</v>
+        <v>133952931</v>
       </c>
       <c r="B6" t="n">
-        <v>57975</v>
+        <v>5181</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Smedsjön, Vstm</t>
+          <t>Norra Hammarskogen, Norra Hammarskogen, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>503672</v>
+        <v>504125</v>
       </c>
       <c r="R6" t="n">
-        <v>6619237</v>
+        <v>6619259</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1216,17 +1211,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2026-05-31</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
+          <t>2026-05-30</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,12 +1241,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Per Arneborn</t>
+          <t>Lotta Sörman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 20364-2026 artfynd.xlsx
+++ b/artfynd/A 20364-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133472666</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -926,6 +936,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133951012</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1033,6 +1048,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133952810</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1143,6 +1163,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134220564</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1250,8 +1275,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133952931</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>